--- a/Result/profitability/3555.xlsx
+++ b/Result/profitability/3555.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM70"/>
+  <dimension ref="A1:AM71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.64</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09625</v>
+        <v>1.2525</v>
       </c>
       <c r="N2" t="n">
-        <v>21.09125</v>
+        <v>24.55625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.92</v>
       </c>
       <c r="M3" t="n">
-        <v>0.96125</v>
+        <v>1.0925</v>
       </c>
       <c r="N3" t="n">
-        <v>20.88875</v>
+        <v>24.47</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>-2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0.56625</v>
+        <v>0.8062500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>19.77125</v>
+        <v>25.04625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>3.23</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03375</v>
+        <v>1.25</v>
       </c>
       <c r="N5" t="n">
-        <v>24.1975</v>
+        <v>32.085</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.38</v>
       </c>
       <c r="M6" t="n">
-        <v>1.02625</v>
+        <v>1.1825</v>
       </c>
       <c r="N6" t="n">
-        <v>30.475</v>
+        <v>36.71625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>3.47</v>
       </c>
       <c r="M7" t="n">
-        <v>1.44</v>
+        <v>1.3875</v>
       </c>
       <c r="N7" t="n">
-        <v>36.3175</v>
+        <v>41.24</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>4.66</v>
       </c>
       <c r="M8" t="n">
-        <v>1.79375</v>
+        <v>1.28875</v>
       </c>
       <c r="N8" t="n">
-        <v>41.655</v>
+        <v>43.565</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1412,7 +1412,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -9318,6 +9318,133 @@
       </c>
       <c r="AM70" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>3555</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>178</v>
+      </c>
+      <c r="D71" t="n">
+        <v>75</v>
+      </c>
+      <c r="E71" t="n">
+        <v>103</v>
+      </c>
+      <c r="F71" t="n">
+        <v>57.83</v>
+      </c>
+      <c r="G71" t="n">
+        <v>71</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>40.13%</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>-15</v>
+      </c>
+      <c r="J71" t="n">
+        <v>57</v>
+      </c>
+      <c r="K71" t="n">
+        <v>57</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.0675</v>
+      </c>
+      <c r="N71" t="n">
+        <v>24.5475</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W71" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="X71" t="n">
+        <v>-0.7412844036697248</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0.3591069330199765</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>-5.40625</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>63.09999999999999</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>-11.97343453510437</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK71" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
